--- a/V.1.4/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials-DONGLE01.xlsx
+++ b/V.1.4/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials-DONGLE01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PCB\PRJ_Dongle01\Project Outputs for DONGLE01\Generate Files\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PCB\PRJ_Dongle01\V.1.4\Project Outputs for DONGLE01\Generate Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75683ABD-12DB-4837-A781-2935938050E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08F8DD88-428E-4BFD-99F7-E51B8BCBEA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{3FBA72AC-4AA3-4D1B-B971-8927A82C39CB}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11505" xr2:uid="{31E44B2A-85FC-466C-B159-328529E7D618}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-DONGLE01" sheetId="1" r:id="rId1"/>
@@ -839,7 +839,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5437FA9-F575-4152-997F-513A1E7C8E89}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7F24413-57DC-481B-86FB-FE08735CFE2D}">
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1520,6 +1520,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
--- a/V.1.4/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials-DONGLE01.xlsx
+++ b/V.1.4/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials-DONGLE01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PCB\PRJ_Dongle01\V.1.4\Project Outputs for DONGLE01\Generate Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08F8DD88-428E-4BFD-99F7-E51B8BCBEA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B11FDC5-470C-4912-BA92-5D77E94A01E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11505" xr2:uid="{31E44B2A-85FC-466C-B159-328529E7D618}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{92DA4253-EAAE-4A5E-8D7F-E04E5CC5DE0E}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-DONGLE01" sheetId="1" r:id="rId1"/>
@@ -839,7 +839,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7F24413-57DC-481B-86FB-FE08735CFE2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4007C8D-C2C4-4B7D-A814-FB45619C6D4B}">
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/V.1.4/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials-DONGLE01.xlsx
+++ b/V.1.4/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials-DONGLE01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PCB\PRJ_Dongle01\V.1.4\Project Outputs for DONGLE01\Generate Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B11FDC5-470C-4912-BA92-5D77E94A01E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35C29B10-9E7D-4720-BB60-AFFDC31AEE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{92DA4253-EAAE-4A5E-8D7F-E04E5CC5DE0E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{D72F2A4C-799C-48DB-90E1-35DCA5237302}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-DONGLE01" sheetId="1" r:id="rId1"/>
@@ -839,7 +839,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4007C8D-C2C4-4B7D-A814-FB45619C6D4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F85BB5BE-66EF-4CBE-911E-D17D49C9F4CB}">
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1520,6 +1520,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>